--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487853_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487853_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.625999999999999</v>
+        <v>9.6358</v>
       </c>
       <c r="E2" t="n">
-        <v>8.2834</v>
+        <v>8.7354</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3426</v>
+        <v>0.9004</v>
       </c>
       <c r="G2" t="n">
         <v>8.4992</v>
@@ -610,13 +610,13 @@
         <v>1.0406</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.8149</v>
+        <v>0.1949</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1743</v>
+        <v>0.2777</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.0828</v>
       </c>
       <c r="V2" t="n">
         <v>1.1498</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.27</v>
+        <v>8.011799999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0119</v>
+        <v>5.6363</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2581</v>
+        <v>2.3755</v>
       </c>
       <c r="G3" t="n">
         <v>2.5276</v>
@@ -688,13 +688,13 @@
         <v>0.6244</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2616</v>
+        <v>1.0034</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0033</v>
+        <v>0.6211</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2649</v>
+        <v>0.3824</v>
       </c>
       <c r="V3" t="n">
         <v>3.8564</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7062</v>
+        <v>1.6432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1301</v>
+        <v>0.6014</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8363</v>
+        <v>1.0419</v>
       </c>
       <c r="G4" t="n">
         <v>4.9087</v>
@@ -766,13 +766,13 @@
         <v>1.2487</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8507</v>
+        <v>0.0863</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6277</v>
+        <v>0.1039</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2231</v>
+        <v>-0.0176</v>
       </c>
       <c r="V4" t="n">
         <v>-0.23</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2952</v>
+        <v>-0.3222</v>
       </c>
       <c r="E5" t="n">
-        <v>0.702</v>
+        <v>0.2314</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4068</v>
+        <v>-0.5536</v>
       </c>
       <c r="G5" t="n">
         <v>-0.3001</v>
@@ -844,13 +844,13 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1385</v>
+        <v>0.5211</v>
       </c>
       <c r="T5" t="n">
-        <v>0.972</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1664</v>
+        <v>0.0196</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1618</v>
+        <v>-0.8416</v>
       </c>
       <c r="E6" t="n">
-        <v>1.76</v>
+        <v>1.4619</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9219</v>
+        <v>-2.3035</v>
       </c>
       <c r="G6" t="n">
         <v>1.0451</v>
@@ -922,13 +922,13 @@
         <v>0.8325</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0876</v>
+        <v>0.4078</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4658</v>
+        <v>0.1677</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6218</v>
+        <v>0.2401</v>
       </c>
       <c r="V6" t="n">
         <v>-2.9188</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9147</v>
+        <v>-1.8832</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3578</v>
+        <v>-1.0417</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5569</v>
+        <v>-0.8416</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3691</v>
+        <v>-1.3533</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.8827</v>
+        <v>-0.3923</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5135</v>
+        <v>-0.9609</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0556</v>
+        <v>-1.3165</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.062</v>
+        <v>-0.3882</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1176</v>
+        <v>-0.9283</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4247</v>
+        <v>-0.0368</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8207</v>
+        <v>-0.0041</v>
       </c>
       <c r="O7" t="n">
-        <v>0.396</v>
+        <v>-0.0326</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.6649</v>
+        <v>0.2081</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4162</v>
+        <v>0.2081</v>
       </c>
       <c r="S7" t="n">
-        <v>2.393</v>
+        <v>0.4294</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4378</v>
+        <v>0.2748</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9552</v>
+        <v>0.1546</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2737</v>
+        <v>-1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5036</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>O. OKAFOR</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9192</v>
+        <v>-1.8959</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4885</v>
+        <v>-2.0282</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4307</v>
+        <v>0.1323</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3299</v>
+        <v>-3.0425</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1086</v>
+        <v>-0.1597</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2213</v>
+        <v>-2.8828</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3438</v>
+        <v>-2.8587</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2834</v>
+        <v>0.1343</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0604</v>
+        <v>-2.993</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6737</v>
+        <v>-0.1838</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3921</v>
+        <v>-0.294</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2817</v>
+        <v>0.1102</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6649</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9508</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1646</v>
+        <v>0.2467</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7862</v>
+        <v>0.5461</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8751</v>
+        <v>0.3538</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.7076</v>
+        <v>0.5838</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7485</v>
+        <v>-1.9519</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6427</v>
+        <v>-1.0426</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1058</v>
+        <v>-0.9092</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3533</v>
+        <v>-0.3691</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3923</v>
+        <v>-0.8827</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9609</v>
+        <v>0.5135</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.3165</v>
+        <v>0.0556</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3882</v>
+        <v>-0.062</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.9283</v>
+        <v>0.1176</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0368</v>
+        <v>-0.4247</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0041</v>
+        <v>-0.8207</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0326</v>
+        <v>0.396</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2081</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4358</v>
+        <v>1.3559</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3262</v>
+        <v>0.753</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1096</v>
+        <v>0.6029</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.1675</v>
+        <v>-1.2737</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1675</v>
+        <v>-1.5036</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>O. OKAFOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7722</v>
+        <v>-2.6477</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9926</v>
+        <v>-1.9234</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2204</v>
+        <v>-0.7243000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.0425</v>
+        <v>-0.3299</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1597</v>
+        <v>-0.1086</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.8828</v>
+        <v>-0.2213</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.8587</v>
+        <v>0.3438</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1343</v>
+        <v>0.2834</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.993</v>
+        <v>0.0604</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1838</v>
+        <v>-0.6737</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.294</v>
+        <v>-0.3921</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1102</v>
+        <v>-0.2817</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0835</v>
+        <v>1.2223</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7177</v>
+        <v>0.7297</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6342</v>
+        <v>0.4926</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3538</v>
+        <v>-1.8751</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5838</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5766</v>
+        <v>-2.9653</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9088</v>
+        <v>-1.4149</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6678</v>
+        <v>-1.5504</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5643</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1174</v>
+        <v>0.4939</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3047</v>
+        <v>0.1891</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1873</v>
+        <v>0.3047</v>
       </c>
       <c r="V11" t="n">
         <v>-0.23</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.804399999999998</v>
+        <v>6.782999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>8.236800000000002</v>
+        <v>9.215600000000002</v>
       </c>
       <c r="F12" t="n">
         <v>-2.4325</v>
@@ -1369,7 +1369,7 @@
         <v>4.3691</v>
       </c>
       <c r="L12" t="n">
-        <v>7.082499999999999</v>
+        <v>7.0825</v>
       </c>
       <c r="M12" t="n">
         <v>-1.4302</v>
@@ -1387,22 +1387,22 @@
         <v>-12.4871</v>
       </c>
       <c r="R12" t="n">
-        <v>6.2437</v>
+        <v>6.243699999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5292</v>
+        <v>6.5078</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8863</v>
+        <v>3.8652</v>
       </c>
       <c r="U12" t="n">
-        <v>2.6427</v>
+        <v>2.6426</v>
       </c>
       <c r="V12" t="n">
         <v>-3.5026</v>
       </c>
       <c r="W12" t="n">
-        <v>6.386000000000001</v>
+        <v>6.385999999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-9.8886</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.261</v>
+        <v>1.4142</v>
       </c>
       <c r="E13" t="n">
-        <v>1.8174</v>
+        <v>1.7103</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5564</v>
+        <v>-0.2961</v>
       </c>
       <c r="G13" t="n">
         <v>1.3153</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0522</v>
+        <v>0.101</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3824</v>
+        <v>-0.4895</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3302</v>
+        <v>0.5905</v>
       </c>
       <c r="V13" t="n">
         <v>-1.8751</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8887</v>
+        <v>1.2498</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0429</v>
+        <v>1.2572</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1542</v>
+        <v>-0.0074</v>
       </c>
       <c r="G14" t="n">
         <v>1.018</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.5164</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3262</v>
+        <v>-0.1119</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5513</v>
+        <v>-0.4045</v>
       </c>
       <c r="V14" t="n">
         <v>0.1238</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5885</v>
+        <v>0.6127</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3634</v>
+        <v>-0.9988</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.7749</v>
+        <v>1.6114</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.9283</v>
+        <v>1.0188</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.3649</v>
+        <v>2.5627</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5633</v>
+        <v>-1.5439</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.5645</v>
+        <v>0.4147</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.3482</v>
+        <v>2.5668</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7838000000000001</v>
+        <v>-2.1521</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3638</v>
+        <v>0.6041</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.0167</v>
+        <v>-0.0041</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.3471</v>
+        <v>0.6082</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8325</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0483</v>
+        <v>-0.4061</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0059</v>
+        <v>-0.3729</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0542</v>
+        <v>-0.0332</v>
       </c>
       <c r="V15" t="n">
-        <v>3.7325</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>3.9625</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3103</v>
+        <v>0.0644</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.2131</v>
+        <v>0.9452</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5234</v>
+        <v>-0.8808</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0188</v>
+        <v>-0.3344</v>
       </c>
       <c r="H16" t="n">
-        <v>2.5627</v>
+        <v>0.482</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5439</v>
+        <v>-0.8164</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4147</v>
+        <v>1.5476</v>
       </c>
       <c r="K16" t="n">
-        <v>2.5668</v>
+        <v>1.017</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.1521</v>
+        <v>0.5306999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6041</v>
+        <v>-1.882</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0041</v>
+        <v>-0.5349</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6082</v>
+        <v>-1.3471</v>
       </c>
       <c r="P16" t="n">
+        <v>1.8731</v>
+      </c>
+      <c r="Q16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-1.0406</v>
-      </c>
       <c r="R16" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7085</v>
+        <v>-1.3505</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.7086</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1213</v>
+        <v>-0.6419</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1238</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.1061</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7381</v>
+        <v>-0.0506</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5165999999999999</v>
+        <v>1.2918</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.2546</v>
+        <v>-1.3424</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3344</v>
+        <v>-3.9283</v>
       </c>
       <c r="H17" t="n">
-        <v>0.482</v>
+        <v>-3.3649</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8164</v>
+        <v>-0.5633</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5476</v>
+        <v>-1.5645</v>
       </c>
       <c r="K17" t="n">
-        <v>1.017</v>
+        <v>-2.3482</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.882</v>
+        <v>-2.3638</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5349</v>
+        <v>-1.0167</v>
       </c>
       <c r="O17" t="n">
         <v>-1.3471</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R17" t="n">
         <v>1.8731</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1529</v>
+        <v>-0.6873</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1372</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0157</v>
+        <v>-0.6217</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1238</v>
+        <v>3.7325</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1061</v>
+        <v>3.9625</v>
       </c>
       <c r="X17" t="n">
         <v>-0.23</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5691</v>
+        <v>-1.254</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0354</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5336</v>
+        <v>-1.2185</v>
       </c>
       <c r="G18" t="n">
         <v>-2.0733</v>
@@ -1858,13 +1858,13 @@
         <v>1.8731</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7881</v>
+        <v>-0.473</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4881</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3</v>
+        <v>0.0151</v>
       </c>
       <c r="V18" t="n">
         <v>0.4599</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7063</v>
+        <v>-1.5903</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3322</v>
+        <v>-0.0108</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.374</v>
+        <v>-1.5795</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6435</v>
@@ -1936,13 +1936,13 @@
         <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2297</v>
+        <v>0.3456</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3915</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6211</v>
+        <v>0.4156</v>
       </c>
       <c r="V19" t="n">
         <v>0.1238</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8878</v>
+        <v>-2.1888</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0071</v>
+        <v>-1.1842</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.8807</v>
+        <v>-1.0046</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6347</v>
+        <v>-2.7592</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7953</v>
+        <v>1.1702</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.8394</v>
+        <v>-3.9295</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.01</v>
+        <v>0.1352</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0236</v>
+        <v>2.0399</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9864</v>
+        <v>-1.9047</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6247</v>
+        <v>-2.8944</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7717000000000001</v>
+        <v>-0.8697</v>
       </c>
       <c r="O20" t="n">
-        <v>0.147</v>
+        <v>-2.0247</v>
       </c>
       <c r="P20" t="n">
-        <v>1.2487</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3118</v>
+        <v>-0.6803</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6054</v>
+        <v>-0.4057</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2935</v>
+        <v>-0.2746</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8137</v>
+        <v>1.8751</v>
       </c>
       <c r="W20" t="n">
-        <v>1.3975</v>
+        <v>1.1675</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.2112</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9516</v>
+        <v>-2.6331</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.72</v>
+        <v>-0.5429</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2316</v>
+        <v>-2.0902</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.7592</v>
+        <v>-2.6347</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1702</v>
+        <v>-0.7953</v>
       </c>
       <c r="I21" t="n">
-        <v>-3.9295</v>
+        <v>-1.8394</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1352</v>
+        <v>-2.01</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0399</v>
+        <v>-0.0236</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9047</v>
+        <v>-1.9864</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.8944</v>
+        <v>-0.6247</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8697</v>
+        <v>-0.7717000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0247</v>
+        <v>0.147</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4568</v>
+        <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4431</v>
+        <v>-0.4334</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9415</v>
+        <v>0.0696</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5016</v>
+        <v>-0.503</v>
       </c>
       <c r="V21" t="n">
-        <v>1.8751</v>
+        <v>-0.8137</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7076</v>
+        <v>-2.2112</v>
       </c>
     </row>
     <row r="22">
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.804399999999999</v>
+        <v>-4.3757</v>
       </c>
       <c r="E22" t="n">
-        <v>2.432499999999999</v>
+        <v>2.432400000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-8.236599999999999</v>
+        <v>-6.8081</v>
       </c>
       <c r="G22" t="n">
         <v>-10.0213</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.6529</v>
+        <v>-1.652900000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.368400000000001</v>
+        <v>-8.368399999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>1.430200000000001</v>
+        <v>1.4302</v>
       </c>
       <c r="K22" t="n">
         <v>2.7161</v>
@@ -2158,25 +2158,25 @@
         <v>-4.3692</v>
       </c>
       <c r="O22" t="n">
-        <v>-7.082400000000001</v>
+        <v>-7.0824</v>
       </c>
       <c r="P22" t="n">
-        <v>6.2437</v>
+        <v>6.243699999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-6.2436</v>
+        <v>-6.243599999999999</v>
       </c>
       <c r="R22" t="n">
         <v>12.4873</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.529100000000001</v>
+        <v>-4.1004</v>
       </c>
       <c r="T22" t="n">
         <v>-2.6428</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.8863</v>
+        <v>-1.4577</v>
       </c>
       <c r="V22" t="n">
         <v>3.5025</v>
